--- a/demo_data/sectors/toptan_ticaret/mizan_prior.xlsx
+++ b/demo_data/sectors/toptan_ticaret/mizan_prior.xlsx
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2241649.32</v>
+        <v>2241649.31</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>43948.06</v>
+        <v>43948.04</v>
       </c>
     </row>
     <row r="52">
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>2263968.750000004</v>
+        <v>2263968.76</v>
       </c>
     </row>
     <row r="57">
